--- a/_FACTORY/_LIGNES/_MAYENNE/EXPORT/QUIZ_THEME_EXPORT.xlsx
+++ b/_FACTORY/_LIGNES/_MAYENNE/EXPORT/QUIZ_THEME_EXPORT.xlsx
@@ -987,7 +987,7 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-19</t>
+          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-21</t>
         </is>
       </c>
     </row>
